--- a/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -576,7 +576,7 @@
 </t>
   </si>
   <si>
-    <t>1899: source value from ADERS - 17_Vac4_TypeBrand</t>
+    <t>1899: source value from ADERS - 17_Vac4_TypeBrand (A-17.41)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -906,7 +906,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1900: source value from ADERS - 17_Vac4_Mfgr</t>
+    <t>1900: source value from ADERS - 17_Vac4_Mfgr (A-17.42)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -918,7 +918,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1901: source value from ADERS - 17_Vac4_Lot</t>
+    <t>1901: source value from ADERS - 17_Vac4_Lot (A-17.43)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -964,7 +964,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1903: source value from ADERS - 17_Vac4_Site</t>
+    <t>1903: source value from ADERS - 17_Vac4_Site (A-17.45)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -991,7 +991,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1902: source value from ADERS - 17_Vac4_Route</t>
+    <t>1902: source value from ADERS - 17_Vac4_Route (A-17.44)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1452,7 +1452,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1904: source value from ADERS - 17_Vac4_DoseInSeries</t>
+    <t>1904: source value from ADERS - 17_Vac4_DoseInSeries (A-17.46)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1816,7 +1816,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>\-</t>
+    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,7 +517,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+    <t>A set of codes indicating the current status of an Immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -548,6 +551,9 @@
     <t>example</t>
   </si>
   <si>
+    <t>The reason why a vaccine was not administered.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -560,23 +566,19 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine Product Type (bind to CVX)</t>
+    <t>Vaccine product administered</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">us-core-5
-</t>
-  </si>
-  <si>
-    <t>1899: source value from ADERS - 17_Vac4_TypeBrand (A-17.41)</t>
+    <t>The code for vaccine product administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
+  </si>
+  <si>
+    <t>1899: source value from ADERS - Vac4_TypeBrand (A-17.41)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -597,11 +599,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -859,6 +857,9 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -906,7 +907,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1900: source value from ADERS - 17_Vac4_Mfgr (A-17.42)</t>
+    <t>1900: source value from ADERS - Vac4_Mfgr (A-17.42)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -918,7 +919,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1901: source value from ADERS - 17_Vac4_Lot (A-17.43)</t>
+    <t>1901: source value from ADERS - Vac4_Lot (A-17.43)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -964,7 +965,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1903: source value from ADERS - 17_Vac4_Site (A-17.45)</t>
+    <t>1903: source value from ADERS - Vac4_Site (A-17.45)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -991,7 +992,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1902: source value from ADERS - 17_Vac4_Route (A-17.44)</t>
+    <t>1902: source value from ADERS - Vac4_Route (A-17.44)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1452,7 +1453,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1904: source value from ADERS - 17_Vac4_DoseInSeries (A-17.46)</t>
+    <t>1904: source value from ADERS - Vac4_DoseInSeries (A-17.46)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1791,7 +1792,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1806,7 +1807,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1992,9 +1993,7 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3203,7 +3202,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3249,9 +3248,11 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" s="2"/>
+      <c r="Y12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3290,16 +3291,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3307,10 +3308,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3324,7 +3325,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3333,16 +3334,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3368,11 +3369,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3390,7 +3393,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3411,13 +3414,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3428,10 +3431,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3454,13 +3457,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3487,11 +3490,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3509,7 +3514,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3518,43 +3523,43 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3564,7 +3569,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3630,7 +3635,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>91</v>
@@ -3806,7 +3811,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
@@ -4044,13 +4049,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4182,7 +4187,7 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>228</v>
@@ -4217,7 +4222,7 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y20" t="s" s="2">
         <v>231</v>
@@ -4949,13 +4954,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4973,7 +4978,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5011,10 +5016,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5040,13 +5045,13 @@
         <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5096,7 +5101,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5123,7 +5128,7 @@
         <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5134,10 +5139,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5163,13 +5168,13 @@
         <v>250</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5219,7 +5224,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5234,7 +5239,7 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>80</v>
@@ -5257,10 +5262,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5286,10 +5291,10 @@
         <v>250</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5340,7 +5345,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5355,7 +5360,7 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
@@ -5364,24 +5369,24 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5404,13 +5409,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5461,7 +5466,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5485,10 +5490,10 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5499,10 +5504,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5525,13 +5530,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5558,13 +5563,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5582,7 +5587,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5597,7 +5602,7 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>80</v>
@@ -5606,24 +5611,24 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5646,13 +5651,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5679,13 +5684,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5703,7 +5708,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5718,7 +5723,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
@@ -5727,24 +5732,24 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5767,13 +5772,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5824,7 +5829,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5848,10 +5853,10 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>80</v>
@@ -5862,10 +5867,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5888,13 +5893,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5945,7 +5950,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5966,13 +5971,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5983,10 +5988,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6104,10 +6109,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6227,14 +6232,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6256,10 +6261,10 @@
         <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>140</v>
@@ -6314,7 +6319,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6352,10 +6357,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6378,13 +6383,13 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6411,13 +6416,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6435,7 +6440,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6456,13 +6461,13 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6473,10 +6478,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6499,16 +6504,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6558,7 +6563,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6579,16 +6584,16 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>80</v>
@@ -6596,10 +6601,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6622,13 +6627,13 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6679,7 +6684,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6700,13 +6705,13 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6717,10 +6722,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6743,13 +6748,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6776,13 +6781,13 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6800,7 +6805,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6821,13 +6826,13 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6838,10 +6843,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6864,13 +6869,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6921,7 +6926,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6942,7 +6947,7 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -6959,10 +6964,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6988,20 +6993,20 @@
         <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>80</v>
@@ -7046,7 +7051,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7070,7 +7075,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>134</v>
@@ -7084,10 +7089,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7110,13 +7115,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7143,13 +7148,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7167,7 +7172,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7205,10 +7210,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7231,13 +7236,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7288,7 +7293,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7300,7 +7305,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7326,10 +7331,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7447,10 +7452,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7570,14 +7575,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7599,10 +7604,10 @@
         <v>137</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
@@ -7657,7 +7662,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7695,10 +7700,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7724,10 +7729,10 @@
         <v>250</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7778,7 +7783,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7802,7 +7807,7 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>134</v>
@@ -7816,10 +7821,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7845,10 +7850,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7899,7 +7904,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7937,10 +7942,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7966,10 +7971,10 @@
         <v>214</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8020,7 +8025,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8044,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>134</v>
@@ -8058,10 +8063,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8087,10 +8092,10 @@
         <v>214</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8141,7 +8146,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8165,7 +8170,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8179,10 +8184,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8205,13 +8210,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8238,13 +8243,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8262,7 +8267,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8286,7 +8291,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>134</v>
@@ -8300,10 +8305,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8326,13 +8331,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8359,13 +8364,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8383,7 +8388,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8421,10 +8426,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8447,16 +8452,16 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8506,7 +8511,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8530,10 +8535,10 @@
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8544,10 +8549,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8665,10 +8670,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8788,14 +8793,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8817,10 +8822,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -8875,7 +8880,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8913,10 +8918,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8942,10 +8947,10 @@
         <v>214</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8996,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9020,7 +9025,7 @@
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>210</v>
@@ -9034,10 +9039,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9060,13 +9065,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9117,7 +9122,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9141,10 +9146,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9155,10 +9160,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9184,10 +9189,10 @@
         <v>220</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9238,7 +9243,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9262,10 +9267,10 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9276,10 +9281,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9302,13 +9307,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9359,7 +9364,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9397,10 +9402,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9518,10 +9523,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9641,14 +9646,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9670,10 +9675,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>140</v>
@@ -9728,7 +9733,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9766,10 +9771,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9795,10 +9800,10 @@
         <v>250</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9849,7 +9854,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9887,10 +9892,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9916,10 +9921,10 @@
         <v>243</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9970,7 +9975,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10008,10 +10013,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10034,13 +10039,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10067,13 +10072,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10091,7 +10096,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10129,10 +10134,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10155,16 +10160,16 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10202,7 +10207,7 @@
         <v>80</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
@@ -10212,7 +10217,7 @@
         <v>259</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>91</v>
@@ -10250,13 +10255,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>80</v>
@@ -10281,13 +10286,13 @@
         <v>250</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10337,7 +10342,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -10352,7 +10357,7 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -10375,10 +10380,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10401,16 +10406,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10460,7 +10465,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,10 +517,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A set of codes indicating the current status of an Immunization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,9 +548,6 @@
     <t>example</t>
   </si>
   <si>
-    <t>The reason why a vaccine was not administered.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -566,19 +560,23 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine product administered</t>
+    <t>Vaccine Product Type (bind to CVX)</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>The code for vaccine product administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
-  </si>
-  <si>
-    <t>1899: source value from ADERS - Vac4_TypeBrand (A-17.41)</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-5
+</t>
+  </si>
+  <si>
+    <t>1899: source value from ADERS - 17_Vac4_TypeBrand</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -599,7 +597,11 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -857,9 +859,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -907,7 +906,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1900: source value from ADERS - Vac4_Mfgr (A-17.42)</t>
+    <t>1900: source value from ADERS - 17_Vac4_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -919,7 +918,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1901: source value from ADERS - Vac4_Lot (A-17.43)</t>
+    <t>1901: source value from ADERS - 17_Vac4_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -965,7 +964,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1903: source value from ADERS - Vac4_Site (A-17.45)</t>
+    <t>1903: source value from ADERS - 17_Vac4_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -992,7 +991,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1902: source value from ADERS - Vac4_Route (A-17.44)</t>
+    <t>1902: source value from ADERS - 17_Vac4_Route</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1453,7 +1452,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1904: source value from ADERS - Vac4_DoseInSeries (A-17.46)</t>
+    <t>1904: source value from ADERS - 17_Vac4_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1792,7 +1791,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1807,7 +1806,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1993,7 +1992,9 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3202,7 +3203,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3248,11 +3249,9 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3291,16 +3290,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3308,10 +3307,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3325,7 +3324,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3334,16 +3333,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3369,14 +3368,12 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3393,7 +3390,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3414,13 +3411,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3431,10 +3428,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3457,13 +3454,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3490,13 +3487,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3514,7 +3509,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3523,43 +3518,43 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3569,7 +3564,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3635,7 +3630,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>91</v>
@@ -3811,7 +3806,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
@@ -4049,13 +4044,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4187,7 +4182,7 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>228</v>
@@ -4222,7 +4217,7 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y20" t="s" s="2">
         <v>231</v>
@@ -4954,31 +4949,31 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5016,10 +5011,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5045,13 +5040,13 @@
         <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5101,7 +5096,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5128,7 +5123,7 @@
         <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5139,10 +5134,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5168,13 +5163,13 @@
         <v>250</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5224,7 +5219,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5239,7 +5234,7 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>80</v>
@@ -5262,10 +5257,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5291,10 +5286,10 @@
         <v>250</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5345,7 +5340,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5360,33 +5355,33 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5409,13 +5404,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5466,7 +5461,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5490,10 +5485,10 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5504,10 +5499,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5530,13 +5525,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5563,14 +5558,14 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5587,7 +5582,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5602,33 +5597,33 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5651,13 +5646,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5684,14 +5679,14 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5708,7 +5703,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5723,33 +5718,33 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5772,13 +5767,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5829,7 +5824,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5853,10 +5848,10 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>80</v>
@@ -5867,10 +5862,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5893,13 +5888,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5950,7 +5945,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5971,13 +5966,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5988,10 +5983,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6109,10 +6104,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6232,14 +6227,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6261,10 +6256,10 @@
         <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>140</v>
@@ -6319,7 +6314,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6357,10 +6352,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6383,13 +6378,13 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6416,14 +6411,14 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>271</v>
+        <v>177</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6440,7 +6435,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6461,13 +6456,13 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6478,10 +6473,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6504,16 +6499,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6563,7 +6558,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6584,16 +6579,16 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>80</v>
@@ -6601,10 +6596,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6627,13 +6622,13 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6684,7 +6679,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6705,13 +6700,13 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6722,10 +6717,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6748,13 +6743,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6781,14 +6776,14 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6805,7 +6800,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6826,13 +6821,13 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6843,10 +6838,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6869,13 +6864,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6926,7 +6921,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6947,7 +6942,7 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -6964,10 +6959,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6993,20 +6988,20 @@
         <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>80</v>
@@ -7051,7 +7046,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7075,7 +7070,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>134</v>
@@ -7089,10 +7084,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7115,13 +7110,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7148,14 +7143,14 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7172,7 +7167,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7210,10 +7205,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7236,13 +7231,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7293,7 +7288,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7305,7 +7300,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7331,10 +7326,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7452,10 +7447,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7575,14 +7570,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7604,10 +7599,10 @@
         <v>137</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
@@ -7662,7 +7657,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7700,10 +7695,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7729,10 +7724,10 @@
         <v>250</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7783,7 +7778,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7807,7 +7802,7 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>134</v>
@@ -7821,10 +7816,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7850,10 +7845,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7904,7 +7899,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7942,10 +7937,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7971,10 +7966,10 @@
         <v>214</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8025,7 +8020,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8049,7 +8044,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>134</v>
@@ -8063,10 +8058,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8092,10 +8087,10 @@
         <v>214</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8146,7 +8141,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8170,7 +8165,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8184,10 +8179,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8210,13 +8205,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8243,14 +8238,14 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8267,7 +8262,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8291,7 +8286,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>134</v>
@@ -8305,10 +8300,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8331,13 +8326,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8364,14 +8359,14 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8388,7 +8383,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8426,10 +8421,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8452,16 +8447,16 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8511,7 +8506,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8535,10 +8530,10 @@
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8549,10 +8544,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8670,10 +8665,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8793,14 +8788,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8822,10 +8817,10 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
@@ -8880,7 +8875,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8918,10 +8913,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8947,10 +8942,10 @@
         <v>214</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9001,7 +8996,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9025,7 +9020,7 @@
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>210</v>
@@ -9039,10 +9034,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9065,13 +9060,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9122,7 +9117,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9146,10 +9141,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9160,10 +9155,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9189,10 +9184,10 @@
         <v>220</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9243,7 +9238,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9267,10 +9262,10 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9281,10 +9276,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9307,13 +9302,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9364,7 +9359,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9402,10 +9397,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9523,10 +9518,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9646,14 +9641,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9675,10 +9670,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>140</v>
@@ -9733,7 +9728,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9771,10 +9766,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9800,10 +9795,10 @@
         <v>250</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9854,7 +9849,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9892,10 +9887,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9921,10 +9916,10 @@
         <v>243</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9975,7 +9970,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10013,10 +10008,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10039,13 +10034,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10072,14 +10067,14 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>455</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10096,7 +10091,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10134,10 +10129,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10160,16 +10155,16 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10207,7 +10202,7 @@
         <v>80</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
@@ -10217,7 +10212,7 @@
         <v>259</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>91</v>
@@ -10255,13 +10250,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C70" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>80</v>
@@ -10286,13 +10281,13 @@
         <v>250</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10342,7 +10337,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -10357,7 +10352,7 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -10380,10 +10375,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10406,16 +10401,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="N71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10465,7 +10460,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
